--- a/products/seller-profit-tracker/dist/MarginKite-Seller-Profit-Tracker.xlsx
+++ b/products/seller-profit-tracker/dist/MarginKite-Seller-Profit-Tracker.xlsx
@@ -255,6 +255,13 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
+  <dxfs count="1">
+    <dxf>
+      <font>
+        <color rgb="00DDEBF7"/>
+      </font>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <indexedColors>
@@ -832,7 +839,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B1:C42"/>
+  <dimension ref="B1:C44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -884,7 +891,7 @@
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>Upload the .xlsx to Google Drive, open it, then File &gt; Save as Google Sheets. Work in that Google Sheets copy.</t>
+          <t>Sign in to your Google account, open the "make a copy" link in your PDF guide, then click Make a copy. The copy is yours, in your own Google Drive.</t>
         </is>
       </c>
     </row>
@@ -896,275 +903,299 @@
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>Open the .xlsx in Excel 2016 or newer (Windows or Mac). If you see 'Enable Editing', click it.</t>
+          <t>Open the .xlsx in Excel 2016 or newer (Windows or Mac). If you see Enable Editing, click it. There are no macros to allow.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="B11" s="4" t="inlineStr">
+        <is>
+          <t>No link handy?</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="inlineStr">
+        <is>
+          <t>Upload the .xlsx to Google Drive, open it, then choose File &gt; Save as Google Sheets.</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="B12" s="3" t="inlineStr">
+      <c r="B12" s="4" t="inlineStr">
+        <is>
+          <t>Two versions</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="inlineStr">
+        <is>
+          <t>MarginKite-Seller-Profit-Tracker.xlsx comes with sample data so you can see it working. MarginKite-Seller-Profit-Tracker-BLANK.xlsx is the same workbook with no sample data, ready for your own. You are in the sample-data version.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="B14" s="3" t="inlineStr">
         <is>
           <t>5 steps to your first result</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="B13" s="4" t="inlineStr">
-        <is>
-          <t>Step 1</t>
-        </is>
-      </c>
-      <c r="C13" s="5" t="inlineStr">
-        <is>
-          <t>Settings: enter your hourly rate, answer the Etsy $10k question, and pick your Shopify plan, billing and payment provider.</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="B14" s="4" t="inlineStr">
-        <is>
-          <t>Step 2</t>
-        </is>
-      </c>
-      <c r="C14" s="5" t="inlineStr">
-        <is>
-          <t>Products: type each product with materials, packaging and labour minutes. Unit cost is worked out for you.</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>Step 3</t>
+          <t>Step 1</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
-          <t>Price Calculator: pick a product and enter price, shipping charged and shipping cost. Read Etsy vs Shopify profit, the price for your target margin, and when Shopify pays off.</t>
+          <t>Settings: enter your hourly rate, answer the Etsy $10k question, and pick your Shopify plan, billing and payment provider.</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="B16" s="4" t="inlineStr">
         <is>
-          <t>Step 4</t>
+          <t>Step 2</t>
         </is>
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>Orders Log: add one row per order (yellow columns A-L). Fees and profit fill in automatically.</t>
+          <t>Products: type each product with materials, packaging and labour minutes. Unit cost is worked out for you.</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="B17" s="4" t="inlineStr">
         <is>
+          <t>Step 3</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="inlineStr">
+        <is>
+          <t>Price Calculator: pick a product and enter price, shipping charged and shipping cost. Read Etsy vs Shopify profit, the price for your target margin, and when Shopify pays off.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="B18" s="4" t="inlineStr">
+        <is>
+          <t>Step 4</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="inlineStr">
+        <is>
+          <t>Orders Log: add one row per order (yellow columns A-L). Fees and profit fill in automatically.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="B19" s="4" t="inlineStr">
+        <is>
           <t>Step 5</t>
         </is>
       </c>
-      <c r="C17" s="5" t="inlineStr">
+      <c r="C19" s="5" t="inlineStr">
         <is>
           <t>Expenses, then Dashboard: add monthly overhead, set the first month on the Dashboard, and read your monthly profit.</t>
         </is>
       </c>
     </row>
-    <row r="19">
-      <c r="B19" s="3" t="inlineStr">
+    <row r="21">
+      <c r="B21" s="3" t="inlineStr">
         <is>
           <t>Colour key</t>
         </is>
       </c>
     </row>
-    <row r="20">
-      <c r="B20" s="6" t="inlineStr">
+    <row r="22">
+      <c r="B22" s="6" t="inlineStr">
         <is>
           <t>Yellow cell</t>
         </is>
       </c>
-      <c r="C20" t="inlineStr">
+      <c r="C22" t="inlineStr">
         <is>
           <t>You type here (inputs).</t>
         </is>
       </c>
     </row>
-    <row r="21">
-      <c r="B21" s="7" t="inlineStr">
+    <row r="23">
+      <c r="B23" s="7" t="inlineStr">
         <is>
           <t>Blue cell</t>
         </is>
       </c>
-      <c r="C21" t="inlineStr">
+      <c r="C23" t="inlineStr">
         <is>
           <t>Calculated for you and locked, so it can't be overwritten by accident.</t>
         </is>
       </c>
     </row>
-    <row r="22">
-      <c r="B22" s="4" t="inlineStr">
+    <row r="24">
+      <c r="B24" s="4" t="inlineStr">
         <is>
           <t>Unlocking</t>
         </is>
       </c>
-      <c r="C22" s="5" t="inlineStr">
+      <c r="C24" s="5" t="inlineStr">
         <is>
           <t>Sheets are protected with NO password. Excel: Review &gt; Unprotect Sheet. Google Sheets: Data &gt; Protect sheets and ranges, then remove the protection. Edit formulas at your own risk.</t>
         </is>
       </c>
     </row>
-    <row r="24">
-      <c r="B24" s="3" t="inlineStr">
+    <row r="26">
+      <c r="B26" s="3" t="inlineStr">
         <is>
           <t>Delete the sample data</t>
         </is>
       </c>
     </row>
-    <row r="25">
-      <c r="B25" s="4" t="inlineStr"/>
-      <c r="C25" s="5" t="inlineStr">
-        <is>
-          <t>The file ships with 5 sample products, 30 sample orders (Aug-Oct 2026) and 3 months of expenses so you can see it working. To start fresh, select these yellow ranges and press Delete (clear the contents; don't delete rows):</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="B26" s="4" t="inlineStr">
-        <is>
-          <t>Orders Log</t>
-        </is>
-      </c>
-      <c r="C26" s="5" t="inlineStr">
-        <is>
-          <t>A6:L505</t>
-        </is>
-      </c>
-    </row>
     <row r="27">
-      <c r="B27" s="4" t="inlineStr">
-        <is>
-          <t>Expenses</t>
-        </is>
-      </c>
+      <c r="B27" s="4" t="inlineStr"/>
       <c r="C27" s="5" t="inlineStr">
         <is>
-          <t>A6:F65</t>
+          <t>The file ships with 5 sample products, 30 sample orders (Aug-Oct 2026) and 3 months of expenses so you can see it working. To start fresh, select these yellow ranges and press Delete (clear the contents; don't delete rows), or use the BLANK version instead:</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="B28" s="4" t="inlineStr">
         <is>
-          <t>Products</t>
+          <t>Orders Log</t>
         </is>
       </c>
       <c r="C28" s="5" t="inlineStr">
         <is>
-          <t>A5:D54 (after the orders, so nothing points at a missing product)</t>
+          <t>A6:L505</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="B29" s="4" t="inlineStr">
         <is>
-          <t>Dashboard</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C29" s="5" t="inlineStr">
         <is>
-          <t>Set 'First month to show' (C4) to your first month.</t>
+          <t>A6:F65</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="B30" s="4" t="inlineStr">
         <is>
+          <t>Products</t>
+        </is>
+      </c>
+      <c r="C30" s="5" t="inlineStr">
+        <is>
+          <t>A5:D54 (after the orders, so nothing points at a missing product)</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="B31" s="4" t="inlineStr">
+        <is>
+          <t>Dashboard</t>
+        </is>
+      </c>
+      <c r="C31" s="5" t="inlineStr">
+        <is>
+          <t>Set 'First month to show' (C4) to your first month.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="B32" s="4" t="inlineStr">
+        <is>
           <t>Price Calculator</t>
         </is>
       </c>
-      <c r="C30" s="5" t="inlineStr">
+      <c r="C32" s="5" t="inlineStr">
         <is>
           <t>Pick one of your own products in C4.</t>
         </is>
       </c>
     </row>
-    <row r="32">
-      <c r="B32" s="3" t="inlineStr">
+    <row r="34">
+      <c r="B34" s="3" t="inlineStr">
         <is>
           <t>Good to know</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="B33" s="4" t="inlineStr">
-        <is>
-          <t>Sales tax</t>
-        </is>
-      </c>
-      <c r="C33" s="5" t="inlineStr">
-        <is>
-          <t>Etsy collects US sales tax for you. It isn't your revenue, so leave it out of every amount.</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="B34" s="4" t="inlineStr">
-        <is>
-          <t>Refunds</t>
-        </is>
-      </c>
-      <c r="C34" s="5" t="inlineStr">
-        <is>
-          <t>Mark Refunded = Y. Leave 'Partial refund $' blank for a full refund. 'Etsy fees credited back?' = Y credits Etsy's % fees in proportion to the refund (see the RULE rows on Settings).</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="B35" s="4" t="inlineStr">
         <is>
-          <t>Offsite Ads</t>
+          <t>Sales tax</t>
         </is>
       </c>
       <c r="C35" s="5" t="inlineStr">
         <is>
-          <t>Set Y only on orders Etsy says came from an Offsite Ad. The 15%/12% rate and the $100 cap come from Settings.</t>
+          <t>Etsy collects US sales tax for you. It isn't your revenue, so leave it out of every amount.</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="B36" s="4" t="inlineStr">
         <is>
+          <t>Refunds</t>
+        </is>
+      </c>
+      <c r="C36" s="5" t="inlineStr">
+        <is>
+          <t>Mark Refunded = Y. Leave 'Partial refund $' blank for a full refund. 'Etsy fees credited back?' = Y credits Etsy's % fees in proportion to the refund (see the RULE rows on Settings).</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="B37" s="4" t="inlineStr">
+        <is>
+          <t>Offsite Ads</t>
+        </is>
+      </c>
+      <c r="C37" s="5" t="inlineStr">
+        <is>
+          <t>Set Y only on orders Etsy says came from an Offsite Ad. The 15%/12% rate and the $100 cap come from Settings.</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="B38" s="4" t="inlineStr">
+        <is>
           <t>Fee changes</t>
         </is>
       </c>
-      <c r="C36" s="5" t="inlineStr">
+      <c r="C38" s="5" t="inlineStr">
         <is>
           <t>Every rate lives in the Settings fee table with its date, source and status. Update a value there and the whole workbook follows. Rows marked UNVERIFIED or ASSUMPTION are best estimates.</t>
         </is>
       </c>
     </row>
-    <row r="38">
-      <c r="B38" s="3" t="inlineStr">
+    <row r="40">
+      <c r="B40" s="3" t="inlineStr">
         <is>
           <t>Disclaimer</t>
         </is>
       </c>
     </row>
-    <row r="39">
-      <c r="B39" s="4" t="inlineStr"/>
-      <c r="C39" s="5" t="inlineStr">
+    <row r="41">
+      <c r="B41" s="4" t="inlineStr"/>
+      <c r="C41" s="5" t="inlineStr">
         <is>
           <t>All figures are estimates. Fees as of 2026-10-21; Etsy fees are not yet verified against Etsy's own fee page. Check your own Etsy and Shopify statements. This is not tax or accounting advice.</t>
         </is>
       </c>
     </row>
-    <row r="41">
-      <c r="B41" s="3" t="inlineStr">
+    <row r="43">
+      <c r="B43" s="3" t="inlineStr">
         <is>
           <t>Made with AI</t>
         </is>
       </c>
     </row>
-    <row r="42">
-      <c r="B42" s="4" t="inlineStr"/>
-      <c r="C42" s="5" t="inlineStr">
+    <row r="44">
+      <c r="B44" s="4" t="inlineStr"/>
+      <c r="C44" s="5" t="inlineStr">
         <is>
           <t>MarginKite is a small shop. AI helped design and build this template; every formula was checked against hand-worked examples before release.</t>
         </is>
@@ -4722,7 +4753,11 @@
       <c r="C6" s="12" t="n">
         <v>32</v>
       </c>
-      <c r="E6" s="9" t="inlineStr"/>
+      <c r="E6" s="9" t="inlineStr">
+        <is>
+          <t>Results appear once you enter a price.</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="B7" s="11" t="inlineStr">
@@ -5149,6 +5184,26 @@
     <mergeCell ref="B39:E39"/>
     <mergeCell ref="B40:E40"/>
   </mergeCells>
+  <conditionalFormatting sqref="C14:D27">
+    <cfRule type="expression" priority="1" dxfId="0" stopIfTrue="0">
+      <formula>$C$6=""</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C31:D31">
+    <cfRule type="expression" priority="1" dxfId="0" stopIfTrue="0">
+      <formula>$C$6=""</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C34:C38">
+    <cfRule type="expression" priority="1" dxfId="0" stopIfTrue="0">
+      <formula>$C$6=""</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B39:E39">
+    <cfRule type="expression" priority="1" dxfId="0" stopIfTrue="0">
+      <formula>$C$6=""</formula>
+    </cfRule>
+  </conditionalFormatting>
   <dataValidations count="2">
     <dataValidation sqref="C4" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Pick from the list" error="Please pick a value from the list." type="list">
       <formula1>Products!$A$5:$A$54</formula1>
